--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5732,6 +5732,22 @@
         <v>1935.4</v>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>345</v>
+      </c>
+      <c r="C333" t="n">
+        <v>757590</v>
+      </c>
+      <c r="D333" t="n">
+        <v>2195.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D333"/>
+  <dimension ref="A1:D334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5748,6 +5748,22 @@
         <v>2195.91</v>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>489</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1108990</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2267.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:D335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5764,6 +5764,22 @@
         <v>2267.87</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>464</v>
+      </c>
+      <c r="C335" t="n">
+        <v>1218650</v>
+      </c>
+      <c r="D335" t="n">
+        <v>2626.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D335"/>
+  <dimension ref="A1:D336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5780,6 +5780,22 @@
         <v>2626.4</v>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>299</v>
+      </c>
+      <c r="C336" t="n">
+        <v>665950</v>
+      </c>
+      <c r="D336" t="n">
+        <v>2227.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5796,6 +5796,22 @@
         <v>2227.26</v>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>453</v>
+      </c>
+      <c r="C337" t="n">
+        <v>997650</v>
+      </c>
+      <c r="D337" t="n">
+        <v>2202.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D337"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5812,6 +5812,22 @@
         <v>2202.32</v>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>429</v>
+      </c>
+      <c r="C338" t="n">
+        <v>1151910</v>
+      </c>
+      <c r="D338" t="n">
+        <v>2685.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5828,6 +5828,22 @@
         <v>2685.1</v>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>327</v>
+      </c>
+      <c r="C339" t="n">
+        <v>749430</v>
+      </c>
+      <c r="D339" t="n">
+        <v>2291.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:D340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5844,6 +5844,22 @@
         <v>2291.83</v>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>454</v>
+      </c>
+      <c r="C340" t="n">
+        <v>1013660</v>
+      </c>
+      <c r="D340" t="n">
+        <v>2232.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D340"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5860,6 +5860,22 @@
         <v>2232.73</v>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>572</v>
+      </c>
+      <c r="C341" t="n">
+        <v>1341700</v>
+      </c>
+      <c r="D341" t="n">
+        <v>2345.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:D342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5876,6 +5876,22 @@
         <v>2345.63</v>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>528</v>
+      </c>
+      <c r="C342" t="n">
+        <v>1336850</v>
+      </c>
+      <c r="D342" t="n">
+        <v>2531.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D342"/>
+  <dimension ref="A1:D343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5892,6 +5892,22 @@
         <v>2531.91</v>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>772</v>
+      </c>
+      <c r="C343" t="n">
+        <v>1566540</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2029.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5908,6 +5908,22 @@
         <v>2029.2</v>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>266</v>
+      </c>
+      <c r="C344" t="n">
+        <v>581280</v>
+      </c>
+      <c r="D344" t="n">
+        <v>2185.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D344"/>
+  <dimension ref="A1:D345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5924,6 +5924,22 @@
         <v>2185.26</v>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>384</v>
+      </c>
+      <c r="C345" t="n">
+        <v>877080</v>
+      </c>
+      <c r="D345" t="n">
+        <v>2284.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D345"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5940,6 +5940,22 @@
         <v>2284.06</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>315</v>
+      </c>
+      <c r="C346" t="n">
+        <v>695160</v>
+      </c>
+      <c r="D346" t="n">
+        <v>2206.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5956,6 +5956,22 @@
         <v>2206.86</v>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>387</v>
+      </c>
+      <c r="C347" t="n">
+        <v>971270</v>
+      </c>
+      <c r="D347" t="n">
+        <v>2509.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D347"/>
+  <dimension ref="A1:D348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5972,6 +5972,22 @@
         <v>2509.74</v>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>821</v>
+      </c>
+      <c r="C348" t="n">
+        <v>1829070</v>
+      </c>
+      <c r="D348" t="n">
+        <v>2227.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D348"/>
+  <dimension ref="A1:D349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5988,6 +5988,22 @@
         <v>2227.86</v>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>952</v>
+      </c>
+      <c r="C349" t="n">
+        <v>1845150</v>
+      </c>
+      <c r="D349" t="n">
+        <v>1938.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6004,6 +6004,22 @@
         <v>1938.18</v>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>304</v>
+      </c>
+      <c r="C350" t="n">
+        <v>592890</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1950.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D350"/>
+  <dimension ref="A1:D351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6020,6 +6020,22 @@
         <v>1950.3</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>298</v>
+      </c>
+      <c r="C351" t="n">
+        <v>731330</v>
+      </c>
+      <c r="D351" t="n">
+        <v>2454.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D351"/>
+  <dimension ref="A1:D352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6036,6 +6036,22 @@
         <v>2454.13</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>491</v>
+      </c>
+      <c r="C352" t="n">
+        <v>1238020</v>
+      </c>
+      <c r="D352" t="n">
+        <v>2521.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D352"/>
+  <dimension ref="A1:D353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6052,6 +6052,22 @@
         <v>2521.43</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>402</v>
+      </c>
+      <c r="C353" t="n">
+        <v>1232570</v>
+      </c>
+      <c r="D353" t="n">
+        <v>3066.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D353"/>
+  <dimension ref="A1:D354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6068,6 +6068,22 @@
         <v>3066.09</v>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>365</v>
+      </c>
+      <c r="C354" t="n">
+        <v>801940</v>
+      </c>
+      <c r="D354" t="n">
+        <v>2197.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D354"/>
+  <dimension ref="A1:D355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6084,6 +6084,22 @@
         <v>2197.1</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>596</v>
+      </c>
+      <c r="C355" t="n">
+        <v>1237090</v>
+      </c>
+      <c r="D355" t="n">
+        <v>2075.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6100,6 +6100,22 @@
         <v>2075.65</v>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>339</v>
+      </c>
+      <c r="C356" t="n">
+        <v>861640</v>
+      </c>
+      <c r="D356" t="n">
+        <v>2541.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6116,6 +6116,22 @@
         <v>2541.71</v>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>777</v>
+      </c>
+      <c r="C357" t="n">
+        <v>1877730</v>
+      </c>
+      <c r="D357" t="n">
+        <v>2416.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D357"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6132,6 +6132,22 @@
         <v>2416.64</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>911</v>
+      </c>
+      <c r="C358" t="n">
+        <v>2170310</v>
+      </c>
+      <c r="D358" t="n">
+        <v>2382.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D358"/>
+  <dimension ref="A1:D359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6148,6 +6148,22 @@
         <v>2382.34</v>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>337</v>
+      </c>
+      <c r="C359" t="n">
+        <v>854240</v>
+      </c>
+      <c r="D359" t="n">
+        <v>2534.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D359"/>
+  <dimension ref="A1:D360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6164,6 +6164,22 @@
         <v>2534.84</v>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>334</v>
+      </c>
+      <c r="C360" t="n">
+        <v>825120</v>
+      </c>
+      <c r="D360" t="n">
+        <v>2470.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D360"/>
+  <dimension ref="A1:D361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6180,6 +6180,22 @@
         <v>2470.42</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>423</v>
+      </c>
+      <c r="C361" t="n">
+        <v>1372980</v>
+      </c>
+      <c r="D361" t="n">
+        <v>3245.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D361"/>
+  <dimension ref="A1:D362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6196,6 +6196,22 @@
         <v>3245.82</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>758</v>
+      </c>
+      <c r="C362" t="n">
+        <v>2207070</v>
+      </c>
+      <c r="D362" t="n">
+        <v>2911.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6212,6 +6212,22 @@
         <v>2911.7</v>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>459</v>
+      </c>
+      <c r="C363" t="n">
+        <v>884960</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1928.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D363"/>
+  <dimension ref="A1:D364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6228,6 +6228,22 @@
         <v>1928.02</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>217</v>
+      </c>
+      <c r="C364" t="n">
+        <v>540530</v>
+      </c>
+      <c r="D364" t="n">
+        <v>2490.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D364"/>
+  <dimension ref="A1:D365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6244,6 +6244,22 @@
         <v>2490.92</v>
       </c>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>272</v>
+      </c>
+      <c r="C365" t="n">
+        <v>660970</v>
+      </c>
+      <c r="D365" t="n">
+        <v>2430.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D365"/>
+  <dimension ref="A1:D366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6260,6 +6260,22 @@
         <v>2430.04</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>436</v>
+      </c>
+      <c r="C366" t="n">
+        <v>1802430</v>
+      </c>
+      <c r="D366" t="n">
+        <v>4134.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D366"/>
+  <dimension ref="A1:D367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6276,6 +6276,22 @@
         <v>4134.01</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>417</v>
+      </c>
+      <c r="C367" t="n">
+        <v>962080</v>
+      </c>
+      <c r="D367" t="n">
+        <v>2307.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D367"/>
+  <dimension ref="A1:D368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6292,6 +6292,22 @@
         <v>2307.15</v>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>393</v>
+      </c>
+      <c r="C368" t="n">
+        <v>905810</v>
+      </c>
+      <c r="D368" t="n">
+        <v>2304.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D368"/>
+  <dimension ref="A1:D369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6308,6 +6308,22 @@
         <v>2304.86</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1073</v>
+      </c>
+      <c r="C369" t="n">
+        <v>3381860</v>
+      </c>
+      <c r="D369" t="n">
+        <v>3151.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D369"/>
+  <dimension ref="A1:D370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6324,6 +6324,22 @@
         <v>3151.78</v>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>339</v>
+      </c>
+      <c r="C370" t="n">
+        <v>966400</v>
+      </c>
+      <c r="D370" t="n">
+        <v>2850.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D370"/>
+  <dimension ref="A1:D371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6340,6 +6340,22 @@
         <v>2850.74</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>347</v>
+      </c>
+      <c r="C371" t="n">
+        <v>869510</v>
+      </c>
+      <c r="D371" t="n">
+        <v>2505.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D371"/>
+  <dimension ref="A1:D372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6356,6 +6356,22 @@
         <v>2505.79</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>355</v>
+      </c>
+      <c r="C372" t="n">
+        <v>808010</v>
+      </c>
+      <c r="D372" t="n">
+        <v>2276.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D372"/>
+  <dimension ref="A1:D373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6372,6 +6372,22 @@
         <v>2276.08</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>463</v>
+      </c>
+      <c r="C373" t="n">
+        <v>1408160</v>
+      </c>
+      <c r="D373" t="n">
+        <v>3041.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D373"/>
+  <dimension ref="A1:D376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Total rugs sold</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Total sales amount (SEK)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Average order value (SEK)</t>
         </is>
@@ -6386,6 +6398,54 @@
       </c>
       <c r="D373" t="n">
         <v>3041.38</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>309</v>
+      </c>
+      <c r="C374" t="n">
+        <v>757730</v>
+      </c>
+      <c r="D374" t="n">
+        <v>2452.2</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>474</v>
+      </c>
+      <c r="C375" t="n">
+        <v>1050930</v>
+      </c>
+      <c r="D375" t="n">
+        <v>2217.15</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>844</v>
+      </c>
+      <c r="C376" t="n">
+        <v>2109440</v>
+      </c>
+      <c r="D376" t="n">
+        <v>2499.34</v>
       </c>
     </row>
   </sheetData>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D376"/>
+  <dimension ref="A1:D377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total rugs sold</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total sales amount (SEK)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Average order value (SEK)</t>
         </is>
@@ -6446,6 +6434,22 @@
       </c>
       <c r="D376" t="n">
         <v>2499.34</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>466</v>
+      </c>
+      <c r="C377" t="n">
+        <v>1045560</v>
+      </c>
+      <c r="D377" t="n">
+        <v>2243.69</v>
       </c>
     </row>
   </sheetData>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D377"/>
+  <dimension ref="A1:D378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6452,6 +6452,22 @@
         <v>2243.69</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>406</v>
+      </c>
+      <c r="C378" t="n">
+        <v>927060</v>
+      </c>
+      <c r="D378" t="n">
+        <v>2283.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D378"/>
+  <dimension ref="A1:D379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6468,6 +6468,22 @@
         <v>2283.4</v>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>1114</v>
+      </c>
+      <c r="C379" t="n">
+        <v>4679440</v>
+      </c>
+      <c r="D379" t="n">
+        <v>4200.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D379"/>
+  <dimension ref="A1:D380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6484,6 +6484,22 @@
         <v>4200.57</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>869</v>
+      </c>
+      <c r="C380" t="n">
+        <v>2633860</v>
+      </c>
+      <c r="D380" t="n">
+        <v>3030.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rugvista_daily_sales.xlsx
+++ b/data/rugvista_daily_sales.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D380"/>
+  <dimension ref="A1:D381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6500,6 +6500,22 @@
         <v>3030.91</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>537</v>
+      </c>
+      <c r="C381" t="n">
+        <v>1200868</v>
+      </c>
+      <c r="D381" t="n">
+        <v>2236.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
